--- a/AppendixModelTable.xlsx
+++ b/AppendixModelTable.xlsx
@@ -12,7 +12,8 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="16815" windowHeight="7095"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="46">
   <si>
     <t>Temporal</t>
   </si>
@@ -93,6 +94,75 @@
   </si>
   <si>
     <t>sp = c(TRUE, FALSE)</t>
+  </si>
+  <si>
+    <t>StrmSlope</t>
+  </si>
+  <si>
+    <t>WidthM</t>
+  </si>
+  <si>
+    <t>SolMean</t>
+  </si>
+  <si>
+    <t>IP_COHO</t>
+  </si>
+  <si>
+    <t>OUT_DIST</t>
+  </si>
+  <si>
+    <t>StrmPow</t>
+  </si>
+  <si>
+    <t>fSTRM_ORDER2</t>
+  </si>
+  <si>
+    <t>fSTRM_ORDER3</t>
+  </si>
+  <si>
+    <t>fSTRM_ORDER4</t>
+  </si>
+  <si>
+    <t>fSTRM_ORDER5</t>
+  </si>
+  <si>
+    <t>fSTRM_ORDER6</t>
+  </si>
+  <si>
+    <t>fSTRM_ORDER7</t>
+  </si>
+  <si>
+    <t>fSTRM_ORDER8</t>
+  </si>
+  <si>
+    <t>MWMT_Index</t>
+  </si>
+  <si>
+    <t>W3Dppt</t>
+  </si>
+  <si>
+    <t>SprPpt</t>
+  </si>
+  <si>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>Est</t>
+  </si>
+  <si>
+    <t>Est. s.e.</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Juvenile</t>
+  </si>
+  <si>
+    <t>Spawners</t>
+  </si>
+  <si>
+    <t>Intercept</t>
   </si>
 </sst>
 </file>
@@ -148,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -160,6 +230,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -441,6 +520,359 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B1" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="8"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="8"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="1">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1">
+        <v>2.82</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="1">
+        <v>-0.41</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1">
+        <v>-0.12</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="1">
+        <v>-0.04</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.03</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.03</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="1">
+        <v>-0.06</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.03</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1">
+        <v>-0.06</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="1">
+        <v>-1.92</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.31</v>
+      </c>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1">
+        <v>-0.89</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="1">
+        <v>-1.06</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1">
+        <v>-0.48</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="1">
+        <v>-0.22</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1">
+        <v>-0.31</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="1">
+        <v>-0.21</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1">
+        <v>-0.44</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="1">
+        <v>-0.67</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1">
+        <v>-0.61</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="1">
+        <v>-1.76</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0.44</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="1">
+        <v>-4.7</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="1">
+        <v>-0.18</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="C19" s="5">
+        <v>0.04</v>
+      </c>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5">
+        <v>-0.08</v>
+      </c>
+      <c r="F19" s="5">
+        <v>0.12</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="E1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
